--- a/artfynd/A 20780-2025 artfynd.xlsx
+++ b/artfynd/A 20780-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79748713</v>
+        <v>79749703</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778951.0291330179</v>
+        <v>778925</v>
       </c>
       <c r="R2" t="n">
-        <v>7511348.015111709</v>
+        <v>7511294</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79749703</v>
+        <v>79749704</v>
       </c>
       <c r="B3" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778925.2082543923</v>
+        <v>778957</v>
       </c>
       <c r="R3" t="n">
-        <v>7511294.141167698</v>
+        <v>7511337</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +845,9 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79749704</v>
+        <v>79748713</v>
       </c>
       <c r="B4" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778957.1886538863</v>
+        <v>778951</v>
       </c>
       <c r="R4" t="n">
-        <v>7511337.138200345</v>
+        <v>7511348</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +947,9 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-06-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +984,7 @@
         <v>79750471</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778884.1392433872</v>
+        <v>778884</v>
       </c>
       <c r="R5" t="n">
-        <v>7511427.004834898</v>
+        <v>7511427</v>
       </c>
       <c r="S5" t="n">
         <v>30</v>
@@ -1099,19 +1049,9 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 20780-2025 artfynd.xlsx
+++ b/artfynd/A 20780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79749703</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79749704</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79748713</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79750471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>